--- a/generated/sources/reports/apac/japan/国内直営店_月次売上報告_2026年9月度_確定.xlsx
+++ b/generated/sources/reports/apac/japan/国内直営店_月次売上報告_2026年9月度_確定.xlsx
@@ -180,7 +180,7 @@
     <t>J10911A00034-999</t>
   </si>
   <si>
-    <t>MAYA</t>
+    <t>NOVA</t>
   </si>
   <si>
     <t>black</t>
@@ -195,31 +195,31 @@
     <t>J20931A00012-999</t>
   </si>
   <si>
-    <t>MAIRE</t>
+    <t>AUREA</t>
   </si>
   <si>
     <t>I10919B00042-999</t>
   </si>
   <si>
-    <t>TRICOT PADDED CARDIGAN</t>
+    <t>VLOGO PADDED CARDIGAN</t>
   </si>
   <si>
     <t>J20931A00087-999</t>
   </si>
   <si>
-    <t>HERMINE</t>
+    <t>LIVIANA</t>
   </si>
   <si>
     <t>I10919B00011-999</t>
   </si>
   <si>
-    <t>LOGO CARDIGAN</t>
+    <t>VLOGO CARDIGAN</t>
   </si>
   <si>
     <t>J20931A00144-999</t>
   </si>
   <si>
-    <t>BADY</t>
+    <t>ARIA</t>
   </si>
   <si>
     <t>J20931A00012-742</t>
@@ -228,19 +228,19 @@
     <t>J20931A00618-999</t>
   </si>
   <si>
-    <t>ILVARO</t>
+    <t>IRIDIA</t>
   </si>
   <si>
     <t>J10911A00213-999</t>
   </si>
   <si>
-    <t>MONTGENEVRE</t>
+    <t>MONTELUCE</t>
   </si>
   <si>
     <t>J20931A00622-999</t>
   </si>
   <si>
-    <t>AMBRINE</t>
+    <t>AMALIA</t>
   </si>
   <si>
     <t>J20931A00087-742</t>
@@ -249,7 +249,7 @@
     <t>J10911A00088-999</t>
   </si>
   <si>
-    <t>MONTCLA</t>
+    <t>MISTRAL</t>
   </si>
   <si>
     <t>I10919B00042-742</t>
@@ -258,7 +258,7 @@
     <t>J10911A00142-999</t>
   </si>
   <si>
-    <t>KARAKORUM</t>
+    <t>COSIMO</t>
   </si>
   <si>
     <t>J20931A00012-20D</t>
@@ -270,25 +270,25 @@
     <t>J10911A00581-999</t>
   </si>
   <si>
-    <t>ROSIERE</t>
+    <t>RIVIERA</t>
   </si>
   <si>
     <t>J10911A00305-999</t>
   </si>
   <si>
-    <t>TIB</t>
+    <t>VEL</t>
   </si>
   <si>
     <t>J10911A00190-999</t>
   </si>
   <si>
-    <t>ECRINS</t>
+    <t>ETTORE</t>
   </si>
   <si>
     <t>I10914M00061-999</t>
   </si>
   <si>
-    <t>TRAILGRIP GTX</t>
+    <t>VTRACK GTX</t>
   </si>
   <si>
     <t>顧客国籍別構成比（POS登録ベース）・免税比率</t>
@@ -336,16 +336,16 @@
     <t>【気温】9月末〜10月初旬にかけて最高気温27〜29℃の日が続き、ダウンジャケットの動きが鈍い。ニット・カットソー・スニーカーは堅調。</t>
   </si>
   <si>
-    <t>【新作】ILVARO（クロップド）は入荷数が少なく、ブラックは銀座で早期に欠品サイズあり。パウダーピンクは問い合わせ多数。</t>
-  </si>
-  <si>
-    <t>【価格改定】11/1付の価格改定（平均+8%）について、10/9に顧客への告知予定。告知後の駆け込み需要を見込み、MAYA・MAIREの在庫確保をMDへ依頼済み。</t>
-  </si>
-  <si>
-    <t>【品質】TIBベストのファスナー（スライダー）不具合による返品が9月末より発生。本社品質管理部へ報告済み。</t>
-  </si>
-  <si>
-    <t>【POLARIS】Genius POLARISは中国のお客様中心に動きあり、日本人顧客の反応は限定的。</t>
+    <t>【新作】IRIDIA（クロップド）は入荷数が少なく、ブラックは銀座で早期に欠品サイズあり。パウダーピンクは問い合わせ多数。</t>
+  </si>
+  <si>
+    <t>【価格改定】11/1付の価格改定（平均+8%）について、10/9に顧客への告知予定。告知後の駆け込み需要を見込み、NOVA・AUREAの在庫確保をMDへ依頼済み。</t>
+  </si>
+  <si>
+    <t>【品質】VELベストのファスナー（スライダー）不具合による返品が9月末より発生。本社品質管理部へ報告済み。</t>
+  </si>
+  <si>
+    <t>【ASTRA】Couture ASTRAは中国のお客様中心に動きあり、日本人顧客の反応は限定的。</t>
   </si>
   <si>
     <t>※本資料の数値は税込。アジア太平洋本部向けレポート（ユーロ換算）とは定義が異なるためご注意ください。</t>
